--- a/AAII_Financials/Quarterly/SJM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SJM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>SJM</t>
   </si>
@@ -656,503 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2219300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2268100</v>
+      </c>
+      <c r="F8" s="3">
         <v>2339400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2330100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2113300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2143800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2186000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2271200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2125100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2205700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2229200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1938600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1805200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2234800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2216300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2205100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1873000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2033800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2057100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2050000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1858000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1920200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2076700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2034000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1971800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2092000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1972300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1957800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1778900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1902100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2011900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2021500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>1902500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>1781300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>1903300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1923600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>1748900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1783800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>1878800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>1913900</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1354700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1400600</v>
+      </c>
+      <c r="F9" s="3">
         <v>1489300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1437200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1623200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1323100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1306800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1379800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1322600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1289500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1406100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1214400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1150400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1440900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1459500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1501200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1319400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1364100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1367200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1332400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1214000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1184500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1267300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1215800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1196400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1303600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1212300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1203800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1079300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1209700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1238100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1250200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1224300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1086900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>1174800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>1168600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>1086800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>1131300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>1155900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>1171000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>864600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>867500</v>
+      </c>
+      <c r="F10" s="3">
         <v>850100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>892900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>490100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>820700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>879200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>891400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>802500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>916200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>823100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>724200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>654800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>793900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>756800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>703900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>553600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>669700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>689900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>717600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>644000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>735700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>809400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>818200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>775400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>788400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>760000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>754000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>699600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>692400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>773800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>771300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>678200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>694400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>728500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>755000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>662100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>652500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>722900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>742900</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,52 +1218,54 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>55200</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>51700</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>51700</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
-        <v>49100</v>
+      <c r="K12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
+      <c r="M12" s="3">
+        <v>49100</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
-        <v>47300</v>
+      <c r="O12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
+      <c r="Q12" s="3">
+        <v>47300</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,246 +1464,264 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-114400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F14" s="3">
         <v>996900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>29500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>21400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>984500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1033600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>276800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>12400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>51100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>127300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>40500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1025800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>1600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>5900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>149600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>14300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>13300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>22800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1700</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>6600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>55700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>3300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>3300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>110000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>125000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>7700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>182500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>9700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>27100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>73300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>93700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AQ14" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>59900</v>
+      </c>
+      <c r="F15" s="3">
         <v>50300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>50200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>50200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>53600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>53900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>55800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>56000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>56000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>55700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>39600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>39800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>40100</v>
-      </c>
-      <c r="P15" s="3">
-        <v>55600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>55600</v>
       </c>
       <c r="R15" s="3">
         <v>55600</v>
       </c>
       <c r="S15" s="3">
+        <v>55600</v>
+      </c>
+      <c r="T15" s="3">
+        <v>55600</v>
+      </c>
+      <c r="U15" s="3">
         <v>57500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>55300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>55400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>55400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>56900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>57000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>59500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>59600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>59900</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>58800</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>58800</v>
       </c>
       <c r="AD15" s="3">
         <v>58800</v>
       </c>
       <c r="AE15" s="3">
+        <v>58800</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>58800</v>
+      </c>
+      <c r="AG15" s="3">
         <v>60400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>59700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>59700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>60500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>52100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>51600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>51600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>51500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>52100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>51700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AQ15" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1822100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1849500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1900100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1884600</v>
       </c>
-      <c r="F17" s="3">
-        <v>2047700</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>2046300</v>
+      </c>
+      <c r="I17" s="3">
         <v>1761000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1718600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1827100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1765700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1776000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1834300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1619100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1503300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1851400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1898400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1911700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1693300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1731800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1906500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1745100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1605500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1681500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1670500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1653200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1610700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1745300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1683300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1628000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1521300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1748500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1794300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1691000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1675600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1464500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1740600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1592900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1515100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1587100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1641100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>1610600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>397200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>418600</v>
+      </c>
+      <c r="F18" s="3">
         <v>439300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>445500</v>
       </c>
-      <c r="F18" s="3">
-        <v>65600</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>67000</v>
+      </c>
+      <c r="I18" s="3">
         <v>382800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>467400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>444100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>359400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>429700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>394900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>319500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>301900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>383400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>317900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>293400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>179700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>302000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>150600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>304900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>252500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>238700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>406200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>380800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>361100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>346700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>289000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>329800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>257600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>153600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>217600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>330500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>226900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>316800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>162700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>330700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>233800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>196700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>237700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>303300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2055,635 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>900</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="P20" s="3">
+        <v>28800</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>900</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-31800</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-27700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>28800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="R20" s="3">
-        <v>500</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-4200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-32200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-2700</v>
       </c>
       <c r="AB20" s="3">
         <v>-1400</v>
       </c>
       <c r="AC20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>2700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>5500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>453700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>477800</v>
+      </c>
+      <c r="F21" s="3">
         <v>489800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>496700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>115300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>435200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>520400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>498100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>414800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>517500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>478300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>364600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>312900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>422600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>428700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>405300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>290900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>412300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>264300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>425000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>362200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>350400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>515500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>462200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>473400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>457400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>399700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>439600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>365700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>263300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>319700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>434200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>338600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>412800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>262800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>435600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>337000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>306400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>342200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>411300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>87900</v>
+      </c>
+      <c r="F22" s="3">
         <v>94500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>98600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>100200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>94200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>95400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>98700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>100400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>97300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>99800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>35100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>32100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>35300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>37900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>39700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>39100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>38000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>39500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>40300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>43100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>42400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>43500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>45100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>46100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>45600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>45100</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>49100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>49400</v>
       </c>
       <c r="AE22" s="3">
         <v>49100</v>
       </c>
       <c r="AF22" s="3">
+        <v>49400</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>49100</v>
+      </c>
+      <c r="AH22" s="3">
         <v>51600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>53600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>53600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>43100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>41600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>42000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>40300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>40300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>327600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-651900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>318400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-56500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-697100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-662500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>66800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>246000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>313100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>195500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>249400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>238400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-678600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>275400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>252900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>141100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>260200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>109600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>268800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>205200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>193300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>361500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>303500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>313600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>298400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>242500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>279100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>206700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>101900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>157200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>269400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>173100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>264200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>116000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>291800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>189000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>161900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>197600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>265500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="F24" s="3">
         <v>72300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>77100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>31900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>91300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>61000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>68000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>75100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>54500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>54800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-77900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>66900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>61800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>31300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>58100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>39900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>62800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>51300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>46300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>100000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>72700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>76600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>72100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>55100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>67900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>52100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>30400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>35800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>80900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>40100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>78300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>50500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>97200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>62200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>51500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>63000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>388100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-724200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>241300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-43900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-729000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-662300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-24500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>185000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>245100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>120400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>194900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>183600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-600700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>208500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>191100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>109800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>202100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>69700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>206000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>153900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>147000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>261500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>230800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>237000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>226300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>187400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>211200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>154600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>71500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>121400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>188500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>133000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>185900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>65500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>194600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>126800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>110400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>134600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>177300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>388100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-724200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>241300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-43900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-728900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-662300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-24500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>185000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>245100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>120400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>194800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>183500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-599900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>208300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>190800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>109600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>201500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>69600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>205400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>153400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>146400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>260400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>229900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>235900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>225100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>186300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>209900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>153800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>71200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>120800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>187500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>132300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>61100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>193500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>126200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>109800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>134000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,11 +3265,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3160,17 +3280,17 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>765800</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3181,8 +3301,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3551,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>31800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>27700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>800</v>
+      </c>
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>31800</v>
-      </c>
-      <c r="L32" s="3">
-        <v>27700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>4600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>800</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>4200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>32200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>2700</v>
       </c>
       <c r="AB32" s="3">
         <v>1400</v>
       </c>
       <c r="AC32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>2600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>8800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>7500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>3600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>2800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>388100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-724200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>241300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-43900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-729000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-662300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-24500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>185000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>245100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>120400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>194900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>183600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-600700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>208300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>190800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>109600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>201500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>69600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>205400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>153400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>146400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>260400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>229900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>235900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>225100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>186300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>209900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>153800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>71200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>120800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>187500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>132300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>826900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>193500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>126200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>109800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>134000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>388100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-724200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>241300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-43900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-729000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-662300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-24500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>185000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>245100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>120400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>194900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>183600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-600700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>208300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>190800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>109600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>201500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>69600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>205400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>153400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>146400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>260400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>229900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>235900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>225100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>186300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>209900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>153800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>71200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>120800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>187500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>132300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>826900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>193500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>126200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>109800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>134000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4275,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>58600</v>
+      </c>
+      <c r="F41" s="3">
         <v>52800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>62800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>39300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>69900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>47200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>49200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>39500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>62000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>35900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3623900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>241100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>655800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>104200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>27100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>151600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>169900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>284300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>155300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>168800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>334300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>501500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>405600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>396600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>391100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>74400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>48800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>48800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>101300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>206500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>171200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>192000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>192600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>186200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>180300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>183200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>166800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>139600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>121800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4257,19 +4435,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>432700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>459800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>487800</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -4280,11 +4458,11 @@
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -4326,548 +4504,578 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
         <v>9000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>11600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>19600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>8400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>13100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>615700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>656300</v>
+      </c>
+      <c r="F43" s="3">
         <v>645700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>675200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>643200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>619000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>654300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>804600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>734900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>736500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>789600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>587900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>592400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>597600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>533900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>609500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>605000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>524700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>563200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>659100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>566000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>533700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>604900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>577000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>497600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>551400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>477300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>522400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>473700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>503800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>502600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>561900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>504200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>385600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>422700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>481600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>433700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>438700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>421400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>517800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1186500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1126500</v>
+      </c>
+      <c r="F44" s="3">
         <v>1171100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1354200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1386000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1209400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1086300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1084400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1137800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1038900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>987600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1084900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1093400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1009800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1241500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1358400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1312800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1089300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1042100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1100200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1105500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>959900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>897900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>993800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>995000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>895300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>958800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1013300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1013300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>910300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>924700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>966200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1017400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>854400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>909100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1011700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>981300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>905700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>995600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1028400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>131700</v>
+      </c>
+      <c r="F45" s="3">
         <v>119000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>233300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>333400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>248300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>187500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>117300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>168900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>129500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>110900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>134700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>110100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>107700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>148200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>255900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>218300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>226200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>98600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>94200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>112600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>113800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>74400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>90700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>95600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>134900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>92200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>74700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>77700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>109800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>92400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>87900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>92200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>122400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>82900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>100600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>74300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>122200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>121200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1991200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1973100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1988600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2325500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2401900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2146600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1975300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2055500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2081100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1966900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1924000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5864100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2496800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2858700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2027800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2250900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2287700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2010100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1988200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2008800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1952900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1941700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2078700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2067100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1984800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1972700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1602700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1659200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1613500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1625200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1726200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1787200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1805800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1555000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1609900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>1785800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1692100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1641800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>1690900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>1805200</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F47" s="3">
         <v>19300</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
-        <v>20000</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
+      <c r="I47" s="3">
+        <v>20000</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>22100</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
+      <c r="M47" s="3">
+        <v>22100</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>24000</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+        <v>24000</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4887,32 +5095,32 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>38600</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
+      <c r="AC47" s="3">
+        <v>38600</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>40900</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
+      <c r="AG47" s="3">
+        <v>40900</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
@@ -4920,11 +5128,11 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL47" s="3">
         <v>0</v>
@@ -4938,246 +5146,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3202800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3180900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3157300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3178100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3167100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3195000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3173100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3235300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3259800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3247300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3187200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2547700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2458800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2342500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2357200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2285300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2236900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2238200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2108900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2139000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2121900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2143500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2085700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2086100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2086900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2117800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2079700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2068700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2058400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1912400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1847900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1818700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1827900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1729100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1633700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1615700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>1595700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>1617500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>1574300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10825000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10888700</v>
+      </c>
+      <c r="F49" s="3">
         <v>10947900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11954100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12006200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>12056900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>13080800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>14175700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>14849100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>14905300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>14978100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9562500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>9612200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9646200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>11494500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>11544900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>11613700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>11668000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>11727800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>11952700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>12006200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>12064800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>12116300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>12624600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>12682300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>12733500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>12804200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>12916300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>12974400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>13029700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>13197900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>13400200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>13717000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>11858700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>11920200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>12137600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>12196400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>12227000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>12346700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>12467300</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>184200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>158200</v>
+      </c>
+      <c r="F52" s="3">
         <v>152600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>170600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>166700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>144800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>196400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>553600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>158200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>132100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>157900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>149400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>144000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>120000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>138000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>138200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>138400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>138700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>141500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>140300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>130700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>134200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>148700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>151900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>148300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>107800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>149600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>146800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>145300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>103100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>155600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>168100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>162300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>158400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>165400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>162900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>157400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>153400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>199800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>199000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16203200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16219400</v>
+      </c>
+      <c r="F54" s="3">
         <v>16265700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>17628300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>17741900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>17563300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18425600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20020100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20348200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>20273700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>20247200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18123700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14711800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14991400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>16017500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16219300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>16276700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>16055000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15966400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>16240800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>16211700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>16284200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>16429400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>16929700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>16902300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>16970400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>16636200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>16791000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>16791600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>16711300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>16927600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>17174200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>17513000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>15301200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>15329200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>15702000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>15641600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>15639700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>15811700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>16058200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +6115,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1205100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1175100</v>
+      </c>
+      <c r="F57" s="3">
         <v>1125600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1109700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1234100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1288700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1133300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1233800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1244100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1336200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1252700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1250300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1301000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1392600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1260600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1242600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1193300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1006800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1031000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1041200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1034100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>896700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>857200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>780600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>782000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>575000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>521800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>503100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>591000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>519600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>552400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>532100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>512100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>471200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>507400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>477600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>477200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>428500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>435800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>380500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>604800</v>
+      </c>
+      <c r="F58" s="3">
         <v>523700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>787100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>990400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>681600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1502900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1532000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1739500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1633600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>461000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>35400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>37100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>34400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>303400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>389400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>181400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>95400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>321500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1119100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1236700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>923400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>697900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>250200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>812000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1129800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1097400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1224500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>803300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>390000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>530000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>144000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>254000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>963500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>783200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>953000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>142000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>406000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>478400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>467300</v>
+      </c>
+      <c r="F59" s="3">
         <v>509400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>512300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>518800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>374900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>446100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>559400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>578400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>425500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>513800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>363200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>437300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>259100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>508300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>495700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>545200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>578100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>562400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>538000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>602900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>596700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>712300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>596200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>594600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>554900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>690400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>658500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>690300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>526000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>493500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>492100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>481900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>377700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>364700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>383600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>490100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>402400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>426700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>464500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2288800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2538200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2357300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2626400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2953900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2652000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3289400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3563200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3764000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3761100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2467400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1834400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1947200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1986700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1740700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2059700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2177200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1952800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1664600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1890500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2763200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2867500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2532400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2692800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2073100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1587100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2077400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2310100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2290800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2341500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1816400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>1434500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>1544000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>1033800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1089900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>1854500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>1750900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>1832600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>997200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>1306300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6559700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6525000</v>
+      </c>
+      <c r="F61" s="3">
         <v>6974600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7173400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7137500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7130100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6483400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6903400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6918700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6925500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8279200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7910600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4458100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4393600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4315800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4315000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4314300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4313100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4312000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4311400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3519700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3519300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>3918000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3917400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4676000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5376800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>4587000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4588200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4689000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>4686300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>5285800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>5885100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>6184900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>4688000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>4688500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>4294100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>4444800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>4445500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>4945000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>4945400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>57900</v>
+      </c>
+      <c r="F62" s="3">
         <v>156600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>154000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>151100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>51200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>152600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>255800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>155200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>57400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>171200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>166200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>172300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>70200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1626000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1627300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1640900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1649000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1722900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1752500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1758500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1772600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1767400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1804500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1808000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1815600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1801400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1797400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1804100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1713000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1803800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1824600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1853300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1688300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1746600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>2517100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>2514000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>2511400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>2627600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>2626400</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10452400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10675600</v>
+      </c>
+      <c r="F66" s="3">
         <v>11029600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11568100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11816000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11480700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11518300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12387000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12578700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12579800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12687100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11034800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7708400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7700600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7682500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8002000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>8132400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>7914900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>7699500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>7954400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8041400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>8159400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8217800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8414700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8557100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>8779500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>8465800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>8695700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>8783900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>8740800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>8906000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>9144200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>9582200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>7410100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>7525000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>8665700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>8709700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>8789500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>8569800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>8878100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-101300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-372800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>468200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>343500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>501800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1345100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2121800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2259900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2188100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2055000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2051100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1964800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2132100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3076200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2976000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2893400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2893000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2955500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2992800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2893800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2847500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2896100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3010900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2882300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2746800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2620500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2533000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2421900</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>2367600</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>2392600</v>
       </c>
       <c r="AG72" s="3">
         <v>2367600</v>
       </c>
       <c r="AH72" s="3">
+        <v>2392600</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>2367600</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>2275600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>2239200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>2126700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1383800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1277800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1240500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>1480700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>1433400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5750800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5543800</v>
+      </c>
+      <c r="F76" s="3">
         <v>5236100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6060200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5925900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6082600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6907300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7633100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7769500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7693900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7560100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7088900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7003400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7290800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8335000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8217300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8144300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8140100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>8266900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8286400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>8170300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8124800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>8211600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>8515000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>8345200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>8190900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>8170400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>8095300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>8007700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7970500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>8021600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>8030000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>7930800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>7891100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>7804200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>7036300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>6931900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>6850200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>7241900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>7180100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>388100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-724200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>241300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-43900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-729000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-662300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-24500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>185000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>245100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>120400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>194900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>183600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-600700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>208300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>190800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>109600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>201500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>69600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>205400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>153400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>146400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>260400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>229900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>235900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>225100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>186300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>209900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>153800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>71200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>120800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>187500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>132300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>826900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>193500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>126200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>109800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>134000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8960,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>69800</v>
+      </c>
+      <c r="F83" s="3">
         <v>68200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>72200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>73000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>69000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>67500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>53000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>50200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>52100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>59800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>57100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>55100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>56600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>115400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>112700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>110700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>114100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>115200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>115900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>113900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>114700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>110500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>113600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>113700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>113400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>112100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>111400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>109600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>112300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>110900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>111200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>111900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>101200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>103700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>102200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>106000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>104200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>104300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9706,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>425700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>579200</v>
+      </c>
+      <c r="F89" s="3">
         <v>558500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>346500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>393900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>239400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>404200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>172900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>428100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>406500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>176900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>217900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>443800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>584600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>205000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-39000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>393700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>439700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>165100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>137800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>291000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>486300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>378700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>409000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>287700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>521600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>224000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>221500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>274200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>421100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>202900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>243000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>314400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>469000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>130300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>304300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>264200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>419500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>136400</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9880,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-95300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-71500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-66300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-84300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-95000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-88100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-87000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-123700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-130600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-156900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-148700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-150300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-145100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-141900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-102100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-88300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-173000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-117300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-59200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-68000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-108000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-69700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-52400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-76600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-76400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-63400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-92600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-88100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-77800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-101300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-80300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-60400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-69600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-55800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-52600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10251,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="F94" s="3">
         <v>16100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>7900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-197900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-81800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>207200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-53300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-172400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-103400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-3567500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-141800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-151900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>563000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-97500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-137800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-71500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-223600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>11100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-63000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-80000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-108000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>520000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-51700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-49200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-93900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-73400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-52100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-52100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-101400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-103900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>312600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-2031500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-105800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-65500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-68200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-38100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-41600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-33800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,82 +10425,84 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>116700</v>
+        <v>116800</v>
       </c>
       <c r="E96" s="3">
         <v>116800</v>
       </c>
       <c r="F96" s="3">
-        <v>114400</v>
+        <v>116700</v>
       </c>
       <c r="G96" s="3">
-        <v>114500</v>
+        <v>116800</v>
       </c>
       <c r="H96" s="3">
         <v>114400</v>
       </c>
       <c r="I96" s="3">
+        <v>114500</v>
+      </c>
+      <c r="J96" s="3">
         <v>114400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
+        <v>114400</v>
+      </c>
+      <c r="L96" s="3">
         <v>112100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>112000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>112300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>108000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>105200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>108400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-108300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-108400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-105100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-107000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-107000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-106900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-97200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-98400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-102400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-102300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-100100</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-100100</v>
       </c>
       <c r="AB96" s="3">
         <v>-100100</v>
@@ -10045,10 +10511,10 @@
         <v>-100100</v>
       </c>
       <c r="AD96" s="3">
-        <v>-96500</v>
+        <v>-100100</v>
       </c>
       <c r="AE96" s="3">
-        <v>-96500</v>
+        <v>-100100</v>
       </c>
       <c r="AF96" s="3">
         <v>-96500</v>
@@ -10057,31 +10523,37 @@
         <v>-96500</v>
       </c>
       <c r="AH96" s="3">
+        <v>-96500</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>-96500</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-88400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-88900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-88000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-88500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-84900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-87200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-87200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-87100</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10921,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-354000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-488800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-586000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-329700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>178000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-292100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-446900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-340700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-23000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-297900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-428200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3349000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-481300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-455200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-410600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-190700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>91900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-284100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-321600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-115500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-223300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-353300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-914800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-318500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-357300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>127400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-420900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-222600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-274600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-282600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-534300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>1790500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-196800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-404000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-61100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-260100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-193700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-351300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-87900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>600</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>600</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>3100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>4400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>700</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>700</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-3400</v>
       </c>
       <c r="AF101" s="3">
         <v>700</v>
       </c>
       <c r="AG101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>6400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>10300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>1400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>23500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-30600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>22700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-22500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>26100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3588000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3382800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-414700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>551600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>77100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-124500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-18300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-114400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>129000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-13500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-165500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-167200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>95900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>9000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>5500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>316700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>25600</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-52500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-105200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>35300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-20800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>5900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>16400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>27200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>17800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>12200</v>
       </c>
     </row>
